--- a/SensitivityAnalysis/SingleSNP/MR_res_gwas.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_res_gwas.xlsx
@@ -148,7 +148,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9323809980346099</v>
+        <v>-0.9323809980346099</v>
       </c>
       <c r="D2" t="n">
         <v>0.045820190786635344</v>
@@ -232,7 +232,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.6921528210536405</v>
+        <v>1.6921528210536405</v>
       </c>
       <c r="D2" t="n">
         <v>0.3595225540482239</v>
@@ -316,7 +316,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.27563395810363833</v>
+        <v>-0.27563395810363833</v>
       </c>
       <c r="D2" t="n">
         <v>0.13901538756531326</v>
@@ -400,7 +400,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.24816643497435406</v>
+        <v>-0.24816643497435406</v>
       </c>
       <c r="D2" t="n">
         <v>0.18251761660514837</v>
@@ -484,7 +484,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2804275921576147</v>
+        <v>-0.2804275921576147</v>
       </c>
       <c r="D2" t="n">
         <v>0.17017400891615933</v>
@@ -568,7 +568,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.013737764249077224</v>
+        <v>-0.013737764249077224</v>
       </c>
       <c r="D2" t="n">
         <v>0.02224018503427448</v>
@@ -652,34 +652,34 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2612530559417094</v>
+        <v>-0.4482047840467859</v>
       </c>
       <c r="D2" t="n">
-        <v>0.19174536215905277</v>
+        <v>0.15818992378121854</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17304014415208704</v>
+        <v>0.0046065322633917685</v>
       </c>
       <c r="F2" t="n">
         <v>1.0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2612530559417094</v>
+        <v>0.4482047840467859</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.11456785389003404</v>
+        <v>0.13815253343559752</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6370739657734528</v>
+        <v>0.7582570346579742</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2985562312291294</v>
+        <v>1.5654992521020639</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8917514275618965</v>
+        <v>1.1481506682841802</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8909398219572324</v>
+        <v>2.134552525231404</v>
       </c>
     </row>
   </sheetData>
